--- a/docs/MVP 0.9 项目管理/01_需求与版本规划/EOR MVP 1.0 目标版本规划 V1.2.xlsx
+++ b/docs/MVP 0.9 项目管理/01_需求与版本规划/EOR MVP 1.0 目标版本规划 V1.2.xlsx
@@ -4315,7 +4315,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4391,9 +4391,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4426,9 +4423,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4743,7 +4737,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{1FA4C15C-E928-427B-A12E-4DFCA4261080}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{0F1C300E-EF9B-4475-95D1-5F0EB8C716F5}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -4752,7 +4746,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="2"/>
       <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B88A2E14-3092-455D-8EC4-5D4A4051B5D1}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{D0851967-4740-4883-9438-6D44370FC967}">
       <tableStyleElement type="headerRow" dxfId="17"/>
       <tableStyleElement type="totalRow" dxfId="16"/>
       <tableStyleElement type="firstRowStripe" dxfId="15"/>
@@ -5034,325 +5028,325 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="44" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="46" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="46" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="46" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="46" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="46" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="46" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="46" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="46" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="46" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="46" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="46" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" s="46" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="46" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="48" t="s">
+      <c r="E15" s="46" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="48" t="s">
+      <c r="E16" s="46" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="D17" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="48" t="s">
+      <c r="E17" s="46" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="48" t="s">
+      <c r="D18" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="48" t="s">
+      <c r="E18" s="46" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="46" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5367,7 +5361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
@@ -5418,60 +5412,60 @@
       <c r="G3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" ht="19.5" spans="1:8">
+    <row r="4" ht="19.5" hidden="1" spans="1:8">
       <c r="A4" s="2"/>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>74</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28" t="s">
+      <c r="D4" s="26"/>
+      <c r="E4" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="25"/>
-    </row>
-    <row r="5" ht="30" spans="1:8">
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" ht="30" hidden="1" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="25"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" ht="27" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="27" t="s">
         <v>80</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -5480,7 +5474,7 @@
       <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" ht="27" spans="1:8">
       <c r="A7" s="2"/>
@@ -5490,30 +5484,30 @@
       <c r="C7" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="25"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" ht="16.5" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="29" t="s">
         <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="27" t="s">
         <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -5522,7 +5516,7 @@
       <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="H8" s="25"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" ht="135" spans="1:8">
       <c r="A9" s="2" t="s">
@@ -5534,7 +5528,7 @@
       <c r="C9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="26" t="s">
         <v>97</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -5546,7 +5540,7 @@
       <c r="G9" s="2">
         <v>3</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" ht="27" spans="1:8">
       <c r="A10" s="2" t="s">
@@ -5558,17 +5552,17 @@
       <c r="C10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="31" t="s">
         <v>102</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2">
         <v>4</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="2" t="s">
         <v>103</v>
       </c>
     </row>
@@ -5580,15 +5574,15 @@
       <c r="C11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="25"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" ht="27" spans="1:8">
       <c r="A12" s="2"/>
@@ -5598,15 +5592,15 @@
       <c r="C12" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="25"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" ht="40.5" spans="1:8">
       <c r="A13" s="2"/>
@@ -5616,57 +5610,57 @@
       <c r="C13" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="25"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" ht="27" spans="1:8">
       <c r="A14" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="31" t="s">
         <v>102</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2">
         <v>5</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:8">
       <c r="A15" s="2"/>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="25"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" ht="108" spans="1:8">
       <c r="A16" s="2"/>
@@ -5676,117 +5670,117 @@
       <c r="C16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="27" t="s">
         <v>122</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="25"/>
-    </row>
-    <row r="17" ht="19.5" spans="1:8">
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" ht="19.5" hidden="1" spans="1:8">
       <c r="A17" s="2"/>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>123</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28" t="s">
+      <c r="D17" s="26"/>
+      <c r="E17" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="25"/>
-    </row>
-    <row r="18" ht="40.5" spans="1:8">
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" ht="40.5" hidden="1" spans="1:8">
       <c r="A18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G18" s="2"/>
-      <c r="H18" s="25"/>
-    </row>
-    <row r="19" ht="30" spans="1:8">
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" ht="30" hidden="1" spans="1:8">
       <c r="A19" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="25"/>
-    </row>
-    <row r="20" ht="46.5" spans="1:8">
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" ht="46.5" hidden="1" spans="1:8">
       <c r="A20" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="25"/>
-    </row>
-    <row r="21" ht="40.5" spans="1:8">
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" ht="40.5" hidden="1" spans="1:8">
       <c r="A21" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G21" s="2"/>
-      <c r="H21" s="25"/>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" ht="40.5" spans="1:8">
       <c r="A22" s="2" t="s">
@@ -5798,17 +5792,17 @@
       <c r="C22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="31" t="s">
         <v>102</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2">
         <v>6</v>
       </c>
-      <c r="H22" s="25"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" ht="27" spans="1:8">
       <c r="A23" s="2"/>
@@ -5818,51 +5812,51 @@
       <c r="C23" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="25"/>
+      <c r="H23" s="2"/>
     </row>
     <row r="24" ht="27" spans="1:8">
       <c r="A24" s="2"/>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="25"/>
+      <c r="H24" s="2"/>
     </row>
     <row r="25" ht="27" spans="1:8">
       <c r="A25" s="2"/>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="25"/>
+      <c r="H25" s="2"/>
     </row>
     <row r="26" ht="27" spans="1:8">
       <c r="A26" s="2"/>
@@ -5872,37 +5866,37 @@
       <c r="C26" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="25"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" ht="43.5" spans="1:8">
       <c r="A27" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="31" t="s">
         <v>102</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2">
         <v>7</v>
       </c>
-      <c r="H27" s="25"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" ht="16.5" spans="1:8">
       <c r="A28" s="2"/>
@@ -5912,59 +5906,59 @@
       <c r="C28" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E28" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="25"/>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" ht="30" spans="1:8">
       <c r="A29" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="31" t="s">
         <v>102</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2">
         <v>8</v>
       </c>
-      <c r="H29" s="25"/>
+      <c r="H29" s="2"/>
     </row>
     <row r="30" ht="43.5" spans="1:8">
       <c r="A30" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="E30" s="28" t="s">
+      <c r="E30" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2">
         <v>9</v>
       </c>
-      <c r="H30" s="25"/>
+      <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="1" ht="54" spans="1:8">
       <c r="A31" s="2"/>
@@ -5974,29 +5968,29 @@
       <c r="C31" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="27" t="s">
         <v>122</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="25"/>
-    </row>
-    <row r="32" ht="19.5" spans="1:8">
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" ht="19.5" hidden="1" spans="1:8">
       <c r="A32" s="2"/>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="25" t="s">
         <v>171</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="28" t="s">
+      <c r="D32" s="26"/>
+      <c r="E32" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="25"/>
+      <c r="H32" s="2"/>
     </row>
     <row r="33" ht="40.5" spans="1:8">
       <c r="A33" s="2"/>
@@ -6006,139 +6000,139 @@
       <c r="C33" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="25"/>
-    </row>
-    <row r="34" ht="33" spans="1:8">
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" ht="33" hidden="1" spans="1:8">
       <c r="A34" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="F34" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G34" s="2"/>
-      <c r="H34" s="25"/>
-    </row>
-    <row r="35" ht="43.5" spans="1:8">
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" ht="43.5" hidden="1" spans="1:8">
       <c r="A35" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F35" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G35" s="2"/>
-      <c r="H35" s="25"/>
+      <c r="H35" s="2"/>
     </row>
     <row r="36" ht="27" spans="1:8">
       <c r="A36" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="E36" s="28" t="s">
+      <c r="E36" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2">
         <v>10</v>
       </c>
-      <c r="H36" s="25"/>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="1" ht="57" spans="1:8">
       <c r="A37" s="2"/>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="28" t="s">
+      <c r="E37" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="25"/>
-    </row>
-    <row r="38" ht="54" spans="1:8">
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" ht="54" hidden="1" spans="1:8">
       <c r="A38" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G38" s="2"/>
-      <c r="H38" s="25"/>
+      <c r="H38" s="2"/>
     </row>
     <row r="39" ht="81" spans="1:8">
       <c r="A39" s="2"/>
-      <c r="B39" s="30" t="s">
+      <c r="B39" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="E39" s="28" t="s">
+      <c r="E39" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="25"/>
+      <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="1" ht="67.5" spans="1:8">
       <c r="A40" s="2"/>
@@ -6148,15 +6142,15 @@
       <c r="C40" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="E40" s="27" t="s">
         <v>122</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="25"/>
+      <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="1" ht="27" spans="1:8">
       <c r="A41" s="2"/>
@@ -6166,15 +6160,15 @@
       <c r="C41" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="E41" s="28" t="s">
+      <c r="E41" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="25"/>
+      <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="1" ht="16.5" spans="1:8">
       <c r="A42" s="2"/>
@@ -6184,15 +6178,15 @@
       <c r="C42" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="25"/>
+      <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="1" ht="67.5" spans="1:8">
       <c r="A43" s="2"/>
@@ -6202,15 +6196,15 @@
       <c r="C43" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="E43" s="28" t="s">
+      <c r="E43" s="27" t="s">
         <v>122</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="25"/>
+      <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="1" ht="54" spans="1:8">
       <c r="A44" s="2"/>
@@ -6220,15 +6214,15 @@
       <c r="C44" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="27" t="s">
+      <c r="D44" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="E44" s="28" t="s">
+      <c r="E44" s="27" t="s">
         <v>122</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="25"/>
+      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="1" ht="67.5" spans="1:8">
       <c r="A45" s="2"/>
@@ -6238,117 +6232,117 @@
       <c r="C45" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D45" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="E45" s="28" t="s">
+      <c r="E45" s="27" t="s">
         <v>122</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="25"/>
-    </row>
-    <row r="46" ht="24" spans="1:8">
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" ht="24" hidden="1" spans="1:8">
       <c r="A46" s="2"/>
-      <c r="B46" s="26" t="s">
+      <c r="B46" s="25" t="s">
         <v>213</v>
       </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="28" t="s">
+      <c r="D46" s="26"/>
+      <c r="E46" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="25"/>
-    </row>
-    <row r="47" ht="16.5" spans="1:8">
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" ht="16.5" hidden="1" spans="1:8">
       <c r="A47" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="D47" s="28" t="s">
+      <c r="D47" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="E47" s="28" t="s">
+      <c r="E47" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F47" s="31" t="s">
+      <c r="F47" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G47" s="2"/>
-      <c r="H47" s="25"/>
-    </row>
-    <row r="48" ht="30" spans="1:8">
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" ht="30" hidden="1" spans="1:8">
       <c r="A48" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="C48" s="30" t="s">
+      <c r="C48" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="D48" s="28" t="s">
+      <c r="D48" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="E48" s="28" t="s">
+      <c r="E48" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F48" s="31" t="s">
+      <c r="F48" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G48" s="2"/>
-      <c r="H48" s="25"/>
-    </row>
-    <row r="49" ht="27" spans="1:8">
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" ht="27" hidden="1" spans="1:8">
       <c r="A49" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="D49" s="28" t="s">
+      <c r="D49" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="E49" s="28" t="s">
+      <c r="E49" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F49" s="31" t="s">
+      <c r="F49" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G49" s="2"/>
-      <c r="H49" s="25"/>
-    </row>
-    <row r="50" ht="16.5" spans="1:8">
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" ht="16.5" hidden="1" spans="1:8">
       <c r="A50" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="D50" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="E50" s="28" t="s">
+      <c r="E50" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G50" s="2"/>
-      <c r="H50" s="25"/>
+      <c r="H50" s="2"/>
     </row>
     <row r="51" ht="16.5" spans="1:8">
       <c r="A51" s="2"/>
@@ -6358,15 +6352,15 @@
       <c r="C51" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D51" s="27" t="s">
+      <c r="D51" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="E51" s="28" t="s">
+      <c r="E51" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="25"/>
+      <c r="H51" s="2"/>
     </row>
     <row r="52" ht="27" spans="1:8">
       <c r="A52" s="2"/>
@@ -6376,15 +6370,15 @@
       <c r="C52" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="E52" s="28" t="s">
+      <c r="E52" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="25"/>
+      <c r="H52" s="2"/>
     </row>
     <row r="53" ht="27" spans="1:8">
       <c r="A53" s="2"/>
@@ -6394,15 +6388,15 @@
       <c r="C53" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="E53" s="28" t="s">
+      <c r="E53" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="25"/>
+      <c r="H53" s="2"/>
     </row>
     <row r="54" ht="27" spans="1:8">
       <c r="A54" s="2"/>
@@ -6412,73 +6406,73 @@
       <c r="C54" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D54" s="27" t="s">
+      <c r="D54" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="E54" s="28" t="s">
+      <c r="E54" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="25"/>
-    </row>
-    <row r="55" ht="19.5" spans="1:8">
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" ht="19.5" hidden="1" spans="1:8">
       <c r="A55" s="2"/>
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="25" t="s">
         <v>241</v>
       </c>
       <c r="C55" s="2"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="28" t="s">
+      <c r="D55" s="26"/>
+      <c r="E55" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="25"/>
+      <c r="H55" s="2"/>
     </row>
     <row r="56" ht="16.5" spans="1:8">
       <c r="A56" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B56" s="34" t="s">
+      <c r="B56" s="33" t="s">
         <v>243</v>
       </c>
-      <c r="C56" s="30" t="s">
+      <c r="C56" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="D56" s="28" t="s">
+      <c r="D56" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="E56" s="28" t="s">
+      <c r="E56" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2">
         <v>11</v>
       </c>
-      <c r="H56" s="25"/>
+      <c r="H56" s="2"/>
     </row>
     <row r="57" ht="27" spans="1:8">
       <c r="A57" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B57" s="35" t="s">
+      <c r="B57" s="34" t="s">
         <v>246</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="E57" s="28" t="s">
+      <c r="E57" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2">
         <v>12</v>
       </c>
-      <c r="H57" s="25"/>
+      <c r="H57" s="2"/>
     </row>
     <row r="58" ht="40.5" spans="1:8">
       <c r="A58" s="2"/>
@@ -6488,227 +6482,227 @@
       <c r="C58" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D58" s="27" t="s">
+      <c r="D58" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="E58" s="28" t="s">
+      <c r="E58" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="25"/>
+      <c r="H58" s="2"/>
     </row>
     <row r="59" ht="40.5" spans="1:8">
       <c r="A59" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="34" t="s">
         <v>253</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D59" s="27" t="s">
+      <c r="D59" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="E59" s="28" t="s">
+      <c r="E59" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2">
         <v>13</v>
       </c>
-      <c r="H59" s="25"/>
+      <c r="H59" s="2"/>
     </row>
     <row r="60" ht="27" spans="1:8">
       <c r="A60" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="34" t="s">
         <v>257</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="E60" s="28" t="s">
+      <c r="E60" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2">
         <v>14</v>
       </c>
-      <c r="H60" s="25"/>
+      <c r="H60" s="2"/>
     </row>
     <row r="61" ht="16.5" spans="1:8">
       <c r="A61" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B61" s="35" t="s">
+      <c r="B61" s="34" t="s">
         <v>260</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="E61" s="28" t="s">
+      <c r="E61" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2">
         <v>15</v>
       </c>
-      <c r="H61" s="25"/>
-    </row>
-    <row r="62" ht="19.5" spans="1:8">
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" ht="19.5" hidden="1" spans="1:8">
       <c r="A62" s="2"/>
-      <c r="B62" s="26" t="s">
+      <c r="B62" s="25" t="s">
         <v>263</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="28" t="s">
+      <c r="D62" s="26"/>
+      <c r="E62" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="25"/>
-    </row>
-    <row r="63" ht="16.5" spans="1:8">
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" ht="16.5" hidden="1" spans="1:8">
       <c r="A63" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B63" s="36" t="s">
+      <c r="B63" s="35" t="s">
         <v>265</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D63" s="27" t="s">
+      <c r="D63" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="E63" s="28" t="s">
+      <c r="E63" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F63" s="31" t="s">
+      <c r="F63" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G63" s="2"/>
-      <c r="H63" s="25"/>
+      <c r="H63" s="2"/>
     </row>
     <row r="64" ht="27" spans="1:8">
       <c r="A64" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B64" s="34" t="s">
+      <c r="B64" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="C64" s="30" t="s">
+      <c r="C64" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D64" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="E64" s="28" t="s">
+      <c r="E64" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2">
         <v>16</v>
       </c>
-      <c r="H64" s="25"/>
-    </row>
-    <row r="65" ht="33" spans="1:8">
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" ht="33" hidden="1" spans="1:8">
       <c r="A65" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B65" s="29" t="s">
+      <c r="B65" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D65" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="E65" s="28" t="s">
+      <c r="E65" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F65" s="31" t="s">
+      <c r="F65" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G65" s="2"/>
-      <c r="H65" s="25"/>
+      <c r="H65" s="2"/>
     </row>
     <row r="66" ht="43.5" spans="1:8">
       <c r="A66" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B66" s="34" t="s">
+      <c r="B66" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="C66" s="30" t="s">
+      <c r="C66" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D66" s="27" t="s">
         <v>279</v>
       </c>
-      <c r="E66" s="28" t="s">
+      <c r="E66" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2">
         <v>17</v>
       </c>
-      <c r="H66" s="25"/>
-    </row>
-    <row r="67" ht="30" spans="1:8">
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" ht="30" hidden="1" spans="1:8">
       <c r="A67" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B67" s="29" t="s">
+      <c r="B67" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="C67" s="28" t="s">
+      <c r="C67" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="D67" s="28" t="s">
+      <c r="D67" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="E67" s="28" t="s">
+      <c r="E67" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F67" s="31" t="s">
+      <c r="F67" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G67" s="2"/>
-      <c r="H67" s="25"/>
-    </row>
-    <row r="68" ht="76.5" spans="1:8">
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" ht="76.5" hidden="1" spans="1:8">
       <c r="A68" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B68" s="29" t="s">
+      <c r="B68" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="C68" s="28" t="s">
+      <c r="C68" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="D68" s="30" t="s">
+      <c r="D68" s="29" t="s">
         <v>285</v>
       </c>
-      <c r="E68" s="28" t="s">
+      <c r="E68" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F68" s="31" t="s">
+      <c r="F68" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G68" s="2"/>
-      <c r="H68" s="25"/>
+      <c r="H68" s="2"/>
     </row>
     <row r="69" ht="40.5" spans="1:8">
       <c r="A69" s="2"/>
@@ -6718,37 +6712,37 @@
       <c r="C69" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="E69" s="28" t="s">
+      <c r="E69" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="25"/>
+      <c r="H69" s="2"/>
     </row>
     <row r="70" ht="54" spans="1:8">
       <c r="A70" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B70" s="35" t="s">
+      <c r="B70" s="34" t="s">
         <v>290</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D70" s="27" t="s">
+      <c r="D70" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="E70" s="28" t="s">
+      <c r="E70" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2">
         <v>18</v>
       </c>
-      <c r="H70" s="25"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" ht="40.5" spans="1:8">
       <c r="A71" s="2" t="s">
@@ -6760,211 +6754,211 @@
       <c r="C71" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="E71" s="28" t="s">
+      <c r="E71" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2">
         <v>19</v>
       </c>
-      <c r="H71" s="25"/>
-    </row>
-    <row r="72" ht="67.5" spans="1:8">
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" ht="67.5" hidden="1" spans="1:8">
       <c r="A72" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="B72" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="C72" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="D72" s="30" t="s">
+      <c r="D72" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="E72" s="28" t="s">
+      <c r="E72" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F72" s="31" t="s">
+      <c r="F72" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G72" s="2"/>
-      <c r="H72" s="37" t="s">
+      <c r="H72" s="26" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="73" ht="67.5" spans="1:8">
+    <row r="73" ht="67.5" hidden="1" spans="1:8">
       <c r="A73" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B73" s="29" t="s">
+      <c r="B73" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="D73" s="30" t="s">
+      <c r="D73" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="E73" s="28" t="s">
+      <c r="E73" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F73" s="31" t="s">
+      <c r="F73" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G73" s="2"/>
-      <c r="H73" s="37" t="s">
+      <c r="H73" s="26" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="74" ht="19.5" spans="1:8">
+    <row r="74" ht="19.5" hidden="1" spans="1:8">
       <c r="A74" s="2"/>
-      <c r="B74" s="38" t="s">
+      <c r="B74" s="36" t="s">
         <v>305</v>
       </c>
       <c r="C74" s="2"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="28" t="s">
+      <c r="D74" s="26"/>
+      <c r="E74" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="25"/>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" ht="30" spans="1:8">
       <c r="A75" s="2"/>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="C75" s="30" t="s">
+      <c r="C75" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="D75" s="30" t="s">
+      <c r="D75" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="E75" s="28" t="s">
+      <c r="E75" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
-      <c r="H75" s="25"/>
+      <c r="H75" s="2"/>
     </row>
     <row r="76" ht="27" spans="1:8">
       <c r="A76" s="2"/>
-      <c r="B76" s="28" t="s">
+      <c r="B76" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="C76" s="30" t="s">
+      <c r="C76" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="D76" s="28" t="s">
+      <c r="D76" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="E76" s="28" t="s">
+      <c r="E76" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-      <c r="H76" s="25"/>
-    </row>
-    <row r="77" ht="19.5" spans="1:8">
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" ht="19.5" hidden="1" spans="1:8">
       <c r="A77" s="2"/>
-      <c r="B77" s="38" t="s">
+      <c r="B77" s="36" t="s">
         <v>310</v>
       </c>
       <c r="C77" s="2"/>
-      <c r="D77" s="27"/>
-      <c r="E77" s="28" t="s">
+      <c r="D77" s="26"/>
+      <c r="E77" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-      <c r="H77" s="25"/>
-    </row>
-    <row r="78" ht="16.5" spans="1:8">
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" ht="16.5" hidden="1" spans="1:8">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="28" t="s">
+      <c r="D78" s="26"/>
+      <c r="E78" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="H78" s="25"/>
-    </row>
-    <row r="79" ht="19.5" spans="1:8">
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" ht="19.5" hidden="1" spans="1:8">
       <c r="A79" s="2"/>
-      <c r="B79" s="38" t="s">
+      <c r="B79" s="36" t="s">
         <v>311</v>
       </c>
       <c r="C79" s="2"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="28" t="s">
+      <c r="D79" s="26"/>
+      <c r="E79" s="27" t="s">
         <v>75</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
-      <c r="H79" s="25"/>
+      <c r="H79" s="2"/>
     </row>
     <row r="80" ht="67.5" spans="1:8">
       <c r="A80" s="2"/>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="26" t="s">
         <v>312</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D80" s="27" t="s">
+      <c r="D80" s="26" t="s">
         <v>313</v>
       </c>
-      <c r="E80" s="28" t="s">
+      <c r="E80" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="25"/>
+      <c r="H80" s="2"/>
     </row>
     <row r="81" ht="16.5" spans="1:8">
       <c r="A81" s="2"/>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="C81" s="28"/>
-      <c r="D81" s="28" t="s">
+      <c r="C81" s="27"/>
+      <c r="D81" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="E81" s="28" t="s">
+      <c r="E81" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="25"/>
-    </row>
-    <row r="82" ht="27" spans="1:8">
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" ht="27" hidden="1" spans="1:8">
       <c r="A82" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B82" s="39" t="s">
+      <c r="B82" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="C82" s="28" t="s">
+      <c r="C82" s="27" t="s">
         <v>318</v>
       </c>
-      <c r="D82" s="28" t="s">
+      <c r="D82" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="E82" s="28" t="s">
+      <c r="E82" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F82" s="31" t="s">
+      <c r="F82" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G82" s="2"/>
-      <c r="H82" s="25"/>
+      <c r="H82" s="2"/>
     </row>
     <row r="83" ht="16.5" spans="1:8">
       <c r="A83" s="2"/>
@@ -6974,15 +6968,15 @@
       <c r="C83" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D83" s="27">
+      <c r="D83" s="26">
         <v>742830</v>
       </c>
-      <c r="E83" s="28" t="s">
+      <c r="E83" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
-      <c r="H83" s="25"/>
+      <c r="H83" s="2"/>
     </row>
     <row r="84" ht="27" spans="1:8">
       <c r="A84" s="2"/>
@@ -6990,79 +6984,79 @@
         <v>322</v>
       </c>
       <c r="C84" s="2"/>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="E84" s="28" t="s">
+      <c r="E84" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-      <c r="H84" s="25"/>
-    </row>
-    <row r="85" ht="16.5" spans="1:8">
-      <c r="A85" s="40" t="s">
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" ht="16.5" hidden="1" spans="1:8">
+      <c r="A85" s="38" t="s">
         <v>324</v>
       </c>
-      <c r="B85" s="41" t="s">
+      <c r="B85" s="39" t="s">
         <v>325</v>
       </c>
       <c r="C85" s="2"/>
-      <c r="D85" s="27" t="s">
+      <c r="D85" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="E85" s="28" t="s">
+      <c r="E85" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F85" s="31" t="s">
+      <c r="F85" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G85" s="2"/>
-      <c r="H85" s="25"/>
-    </row>
-    <row r="86" ht="54" spans="1:8">
-      <c r="A86" s="40" t="s">
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" ht="54" hidden="1" spans="1:8">
+      <c r="A86" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="B86" s="41" t="s">
+      <c r="B86" s="39" t="s">
         <v>328</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D86" s="27" t="s">
+      <c r="D86" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="E86" s="28" t="s">
+      <c r="E86" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F86" s="31" t="s">
+      <c r="F86" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G86" s="2"/>
-      <c r="H86" s="25"/>
-    </row>
-    <row r="87" ht="16.5" spans="1:8">
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" ht="16.5" hidden="1" spans="1:8">
       <c r="A87" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B87" s="41" t="s">
+      <c r="B87" s="39" t="s">
         <v>331</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D87" s="27" t="s">
+      <c r="D87" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="E87" s="28" t="s">
+      <c r="E87" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F87" s="31" t="s">
+      <c r="F87" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G87" s="2"/>
-      <c r="H87" s="25"/>
+      <c r="H87" s="2"/>
     </row>
     <row r="88" ht="54" spans="1:8">
       <c r="A88" s="2" t="s">
@@ -7074,17 +7068,17 @@
       <c r="C88" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D88" s="27" t="s">
+      <c r="D88" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="E88" s="28" t="s">
+      <c r="E88" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2">
         <v>20</v>
       </c>
-      <c r="H88" s="25"/>
+      <c r="H88" s="2"/>
     </row>
     <row r="89" ht="54" spans="1:8">
       <c r="A89" s="2"/>
@@ -7092,53 +7086,53 @@
         <v>338</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="27" t="s">
+      <c r="D89" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="E89" s="28" t="s">
+      <c r="E89" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="25"/>
+      <c r="H89" s="2"/>
     </row>
     <row r="90" ht="81" spans="1:8">
       <c r="A90" s="2"/>
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="26" t="s">
         <v>340</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="27" t="s">
+      <c r="D90" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="E90" s="28" t="s">
+      <c r="E90" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-      <c r="H90" s="25"/>
-    </row>
-    <row r="91" ht="16.5" spans="1:8">
+      <c r="H90" s="2"/>
+    </row>
+    <row r="91" ht="16.5" hidden="1" spans="1:8">
       <c r="A91" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B91" s="31" t="s">
+      <c r="B91" s="30" t="s">
         <v>343</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D91" s="27" t="s">
+      <c r="D91" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="E91" s="28" t="s">
+      <c r="E91" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F91" s="31" t="s">
+      <c r="F91" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="25"/>
+      <c r="H91" s="2"/>
     </row>
     <row r="92" ht="27" spans="1:8">
       <c r="A92" s="2"/>
@@ -7146,103 +7140,103 @@
         <v>345</v>
       </c>
       <c r="C92" s="2"/>
-      <c r="D92" s="27" t="s">
+      <c r="D92" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="E92" s="28" t="s">
+      <c r="E92" s="27" t="s">
         <v>90</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-      <c r="H92" s="25"/>
+      <c r="H92" s="2"/>
     </row>
     <row r="93" ht="30" spans="1:8">
       <c r="A93" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="C93" s="30" t="s">
+      <c r="C93" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="D93" s="28" t="s">
+      <c r="D93" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="E93" s="28" t="s">
+      <c r="E93" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2">
         <v>21</v>
       </c>
-      <c r="H93" s="25"/>
-    </row>
-    <row r="94" ht="81" spans="1:8">
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" ht="81" hidden="1" spans="1:8">
       <c r="A94" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B94" s="31" t="s">
+      <c r="B94" s="30" t="s">
         <v>351</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D94" s="27" t="s">
+      <c r="D94" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="E94" s="28" t="s">
+      <c r="E94" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="F94" s="31" t="s">
+      <c r="F94" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G94" s="2"/>
-      <c r="H94" s="25"/>
+      <c r="H94" s="2"/>
     </row>
     <row r="95" ht="57" spans="1:8">
       <c r="A95" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="27" t="s">
         <v>355</v>
       </c>
-      <c r="C95" s="30" t="s">
+      <c r="C95" s="29" t="s">
         <v>356</v>
       </c>
-      <c r="D95" s="28" t="s">
+      <c r="D95" s="27" t="s">
         <v>357</v>
       </c>
-      <c r="E95" s="28" t="s">
+      <c r="E95" s="27" t="s">
         <v>102</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2">
         <v>22</v>
       </c>
-      <c r="H95" s="25"/>
-    </row>
-    <row r="96" customFormat="1" ht="27" spans="1:8">
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" customFormat="1" ht="27" hidden="1" spans="1:8">
       <c r="A96" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B96" s="31" t="s">
+      <c r="B96" s="30" t="s">
         <v>359</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D96" s="27" t="s">
+      <c r="D96" s="26" t="s">
         <v>360</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F96" s="31" t="s">
+      <c r="F96" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="25"/>
+      <c r="H96" s="2"/>
     </row>
     <row r="97" customFormat="1" ht="40.5" spans="1:8">
       <c r="A97" s="2"/>
@@ -7252,7 +7246,7 @@
       <c r="C97" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D97" s="27" t="s">
+      <c r="D97" s="26" t="s">
         <v>362</v>
       </c>
       <c r="E97" s="2" t="s">
@@ -7260,7 +7254,7 @@
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="25"/>
+      <c r="H97" s="2"/>
     </row>
     <row r="98" customFormat="1" spans="1:8">
       <c r="A98" s="2"/>
@@ -7278,19 +7272,19 @@
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="25"/>
+      <c r="H98" s="2"/>
     </row>
     <row r="99" customFormat="1" ht="40.5" spans="1:8">
       <c r="A99" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B99" s="27" t="s">
+      <c r="B99" s="26" t="s">
         <v>367</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D99" s="27" t="s">
+      <c r="D99" s="26" t="s">
         <v>368</v>
       </c>
       <c r="E99" s="2" t="s">
@@ -7300,49 +7294,49 @@
       <c r="G99" s="2">
         <v>23</v>
       </c>
-      <c r="H99" s="25" t="s">
+      <c r="H99" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="100" customFormat="1" ht="67.5" spans="1:8">
-      <c r="A100" s="42" t="s">
+    <row r="100" customFormat="1" ht="67.5" hidden="1" spans="1:8">
+      <c r="A100" s="40" t="s">
         <v>370</v>
       </c>
-      <c r="B100" s="43" t="s">
+      <c r="B100" s="41" t="s">
         <v>371</v>
       </c>
       <c r="C100" s="2"/>
-      <c r="D100" s="27" t="s">
+      <c r="D100" s="26" t="s">
         <v>372</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F100" s="31" t="s">
+      <c r="F100" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G100" s="2"/>
-      <c r="H100" s="25"/>
-    </row>
-    <row r="101" customFormat="1" ht="54" spans="1:8">
-      <c r="A101" s="42" t="s">
+      <c r="H100" s="2"/>
+    </row>
+    <row r="101" customFormat="1" ht="54" hidden="1" spans="1:8">
+      <c r="A101" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="B101" s="31" t="s">
+      <c r="B101" s="30" t="s">
         <v>374</v>
       </c>
       <c r="C101" s="2"/>
-      <c r="D101" s="27" t="s">
+      <c r="D101" s="26" t="s">
         <v>375</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F101" s="31" t="s">
+      <c r="F101" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G101" s="2"/>
-      <c r="H101" s="25"/>
+      <c r="H101" s="2"/>
     </row>
     <row r="102" customFormat="1" ht="67.5" spans="1:8">
       <c r="A102" s="2" t="s">
@@ -7354,7 +7348,7 @@
       <c r="C102" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D102" s="27" t="s">
+      <c r="D102" s="26" t="s">
         <v>379</v>
       </c>
       <c r="E102" s="2" t="s">
@@ -7364,7 +7358,7 @@
         <v>98</v>
       </c>
       <c r="G102" s="2"/>
-      <c r="H102" s="25"/>
+      <c r="H102" s="2"/>
     </row>
     <row r="103" customFormat="1" ht="54" spans="1:8">
       <c r="A103" s="2" t="s">
@@ -7376,7 +7370,7 @@
       <c r="C103" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D103" s="27" t="s">
+      <c r="D103" s="26" t="s">
         <v>383</v>
       </c>
       <c r="E103" s="2" t="s">
@@ -7386,51 +7380,51 @@
         <v>86</v>
       </c>
       <c r="G103" s="2"/>
-      <c r="H103" s="25"/>
-    </row>
-    <row r="104" customFormat="1" ht="54" spans="1:8">
+      <c r="H103" s="2"/>
+    </row>
+    <row r="104" customFormat="1" ht="54" hidden="1" spans="1:8">
       <c r="A104" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B104" s="31" t="s">
+      <c r="B104" s="30" t="s">
         <v>385</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D104" s="27" t="s">
+      <c r="D104" s="26" t="s">
         <v>387</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F104" s="31" t="s">
+      <c r="F104" s="30" t="s">
         <v>81</v>
       </c>
       <c r="G104" s="2"/>
-      <c r="H104" s="25"/>
-    </row>
-    <row r="105" customFormat="1" ht="67.5" spans="1:8">
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" customFormat="1" ht="67.5" hidden="1" spans="1:8">
       <c r="A105" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B105" s="29" t="s">
+      <c r="B105" s="28" t="s">
         <v>389</v>
       </c>
-      <c r="C105" s="28" t="s">
+      <c r="C105" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="D105" s="27" t="s">
+      <c r="D105" s="26" t="s">
         <v>390</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F105" s="25" t="s">
+      <c r="F105" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G105" s="25"/>
-      <c r="H105" s="37" t="s">
+      <c r="G105" s="2"/>
+      <c r="H105" s="26" t="s">
         <v>301</v>
       </c>
     </row>
@@ -7438,37 +7432,54 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="27"/>
+      <c r="D106" s="26"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" customFormat="1" spans="1:8">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="27"/>
+      <c r="D107" s="26"/>
       <c r="E107" s="2"/>
     </row>
     <row r="111" ht="19.5" spans="1:8">
-      <c r="B111" s="44" t="s">
+      <c r="B111" s="42" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="112" ht="17.25" spans="1:8">
-      <c r="B112" s="45" t="s">
+      <c r="B112" s="43" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="113" ht="17.25" spans="2:2">
-      <c r="B113" s="45" t="s">
+      <c r="B113" s="43" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="114" ht="17.25" spans="2:2">
-      <c r="B114" s="45" t="s">
+      <c r="B114" s="43" t="s">
         <v>394</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:H105" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="P0"/>
+        <filter val="P1"/>
+        <filter val="P2"/>
+        <filter val="P3"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters blank="1">
+        <filter val="待规划"/>
+        <filter val="待确认"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>

--- a/docs/MVP 0.9 项目管理/01_需求与版本规划/EOR MVP 1.0 目标版本规划 V1.2.xlsx
+++ b/docs/MVP 0.9 项目管理/01_需求与版本规划/EOR MVP 1.0 目标版本规划 V1.2.xlsx
@@ -4737,7 +4737,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{0F1C300E-EF9B-4475-95D1-5F0EB8C716F5}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{63D99CDB-F8A7-40AE-8F08-88A8FB0D3FB6}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -4746,7 +4746,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="2"/>
       <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{D0851967-4740-4883-9438-6D44370FC967}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{44AA5E87-5E20-4CC5-BA8F-147D31C2DB05}">
       <tableStyleElement type="headerRow" dxfId="17"/>
       <tableStyleElement type="totalRow" dxfId="16"/>
       <tableStyleElement type="firstRowStripe" dxfId="15"/>
